--- a/SERVER/docs/Objects to Filter Out.xlsx
+++ b/SERVER/docs/Objects to Filter Out.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\creat\dev\sf-migrator-placeholder-folder\sf-migrator\SERVER\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DBF92F-C74F-49BD-9125-C66F61F5D5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2882102F-6015-4D22-8F3D-82F9E57FAC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667" activeTab="2" xr2:uid="{39EC50EE-9F27-496F-8505-B0DD16AAB274}"/>
   </bookViews>
